--- a/Team-Data/2007-08/2-24-2007-08.xlsx
+++ b/Team-Data/2007-08/2-24-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -772,7 +839,7 @@
         <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -784,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>20</v>
@@ -805,7 +872,7 @@
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.778</v>
+        <v>0.774</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J3" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.473</v>
+        <v>0.471</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
         <v>19.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.385</v>
+        <v>0.379</v>
       </c>
       <c r="O3" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="P3" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T3" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U3" t="n">
         <v>21.7</v>
@@ -900,7 +967,7 @@
         <v>15.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X3" t="n">
         <v>4.4</v>
@@ -912,16 +979,16 @@
         <v>22.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC3" t="n">
         <v>9.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
         <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,10 +1018,10 @@
         <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
@@ -966,7 +1033,7 @@
         <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>22</v>
@@ -975,16 +1042,16 @@
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1136,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
@@ -1151,7 +1218,7 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="n">
         <v>17</v>
@@ -1175,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.407</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.427</v>
@@ -1240,25 +1307,25 @@
         <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R5" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
         <v>14.6</v>
@@ -1273,31 +1340,31 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1318,13 +1385,13 @@
         <v>17</v>
       </c>
       <c r="AO5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>20</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1351,7 +1418,7 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1360,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J6" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
@@ -1431,22 +1498,22 @@
         <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U6" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V6" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
         <v>4.9</v>
@@ -1455,19 +1522,19 @@
         <v>4.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1500,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1512,7 +1579,7 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
@@ -1530,10 +1597,10 @@
         <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
         <v>27</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.661</v>
+        <v>0.655</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1601,13 +1668,13 @@
         <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O7" t="n">
         <v>20.9</v>
       </c>
       <c r="P7" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8179999999999999</v>
@@ -1622,7 +1689,7 @@
         <v>42.6</v>
       </c>
       <c r="U7" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V7" t="n">
         <v>12.8</v>
@@ -1631,13 +1698,13 @@
         <v>6</v>
       </c>
       <c r="X7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y7" t="n">
         <v>4</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA7" t="n">
         <v>21.6</v>
@@ -1646,13 +1713,13 @@
         <v>99.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1676,10 +1743,10 @@
         <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>9</v>
@@ -1700,22 +1767,22 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1855,13 +1922,13 @@
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.732</v>
+        <v>0.727</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
         <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.376</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R9" t="n">
         <v>11.7</v>
       </c>
       <c r="S9" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U9" t="n">
         <v>22.8</v>
       </c>
       <c r="V9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X9" t="n">
         <v>5.3</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,13 +2095,13 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2052,7 +2119,7 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
@@ -2061,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2070,19 +2137,19 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2237,13 +2304,13 @@
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2255,10 +2322,10 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J11" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L11" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M11" t="n">
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="O11" t="n">
         <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.725</v>
+        <v>0.729</v>
       </c>
       <c r="R11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S11" t="n">
         <v>32.2</v>
       </c>
       <c r="T11" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V11" t="n">
         <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>5.3</v>
@@ -2365,28 +2432,28 @@
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
         <v>25</v>
@@ -2395,10 +2462,10 @@
         <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2407,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2416,10 +2483,10 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
         <v>7</v>
@@ -2434,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>5</v>
@@ -2449,7 +2516,7 @@
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>8</v>
@@ -2604,7 +2671,7 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
@@ -2768,13 +2835,13 @@
         <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN13" t="n">
         <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2789,16 +2856,16 @@
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.48</v>
@@ -2875,16 +2942,16 @@
         <v>19.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="P14" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
         <v>10.7</v>
@@ -2896,7 +2963,7 @@
         <v>43.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.8</v>
@@ -2908,22 +2975,22 @@
         <v>5.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>108</v>
+        <v>107.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2956,13 +3023,13 @@
         <v>10</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
@@ -2977,13 +3044,13 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>15</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -3027,85 +3094,85 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M15" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O15" t="n">
         <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R15" t="n">
         <v>10.1</v>
       </c>
       <c r="S15" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U15" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V15" t="n">
         <v>16</v>
       </c>
       <c r="W15" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X15" t="n">
         <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3123,25 +3190,25 @@
         <v>11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3162,13 +3229,13 @@
         <v>29</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3177,7 +3244,7 @@
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3344,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3548,7 @@
         <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3508,7 +3575,7 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR17" t="n">
         <v>10</v>
@@ -3538,7 +3605,7 @@
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.204</v>
+        <v>0.208</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,37 +3658,37 @@
         <v>36.6</v>
       </c>
       <c r="J18" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="N18" t="n">
         <v>0.333</v>
       </c>
       <c r="O18" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R18" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S18" t="n">
         <v>29.9</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U18" t="n">
         <v>19.3</v>
@@ -3633,7 +3700,7 @@
         <v>7.5</v>
       </c>
       <c r="X18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
         <v>5.9</v>
@@ -3642,16 +3709,16 @@
         <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.4</v>
+        <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,13 +3733,13 @@
         <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,7 +3748,7 @@
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3696,10 +3763,10 @@
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AU18" t="n">
         <v>27</v>
@@ -3708,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,10 +3927,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3872,13 +3939,13 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4024,7 +4091,7 @@
         <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
         <v>6</v>
@@ -4039,7 +4106,7 @@
         <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM20" t="n">
         <v>7</v>
@@ -4066,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4078,7 +4145,7 @@
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4090,7 +4157,7 @@
         <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
         <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.304</v>
+        <v>0.309</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
       </c>
       <c r="M21" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="O21" t="n">
         <v>19.2</v>
       </c>
       <c r="P21" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="R21" t="n">
         <v>12.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U21" t="n">
         <v>18.5</v>
       </c>
       <c r="V21" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W21" t="n">
         <v>6.3</v>
@@ -4185,19 +4252,19 @@
         <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>19</v>
@@ -4227,7 +4294,7 @@
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
@@ -4236,7 +4303,7 @@
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR21" t="n">
         <v>7</v>
@@ -4263,13 +4330,13 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
         <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.47</v>
@@ -4328,10 +4395,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O22" t="n">
         <v>21.1</v>
@@ -4346,16 +4413,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T22" t="n">
         <v>42.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="W22" t="n">
         <v>6.2</v>
@@ -4364,25 +4431,25 @@
         <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA22" t="n">
         <v>23.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>10</v>
@@ -4412,7 +4479,7 @@
         <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4421,13 +4488,13 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4439,10 +4506,10 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>18</v>
@@ -4576,7 +4643,7 @@
         <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
         <v>12</v>
@@ -4609,13 +4676,13 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>5</v>
@@ -4633,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4665,97 +4732,97 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>38</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>0.679</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.491</v>
+        <v>0.493</v>
       </c>
       <c r="L24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="N24" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O24" t="n">
         <v>18</v>
       </c>
       <c r="P24" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.788</v>
+        <v>0.792</v>
       </c>
       <c r="R24" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U24" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="V24" t="n">
         <v>13.9</v>
       </c>
       <c r="W24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="X24" t="n">
         <v>7.1</v>
-      </c>
-      <c r="X24" t="n">
-        <v>7</v>
       </c>
       <c r="Y24" t="n">
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.2</v>
+        <v>109.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AD24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE24" t="n">
         <v>3</v>
       </c>
-      <c r="AE24" t="n">
-        <v>4</v>
-      </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -4773,7 +4840,7 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO24" t="n">
         <v>21</v>
@@ -4782,16 +4849,16 @@
         <v>25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4812,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.518</v>
+        <v>0.527</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
@@ -4865,37 +4932,37 @@
         <v>35.5</v>
       </c>
       <c r="J25" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.451</v>
       </c>
       <c r="L25" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>0.379</v>
+        <v>0.375</v>
       </c>
       <c r="O25" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P25" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T25" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
         <v>21.3</v>
@@ -4904,10 +4971,10 @@
         <v>13.2</v>
       </c>
       <c r="W25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
         <v>3.8</v>
@@ -4916,19 +4983,19 @@
         <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4949,13 +5016,13 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>23</v>
@@ -4964,16 +5031,16 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
         <v>18</v>
@@ -4988,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -4997,7 +5064,7 @@
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.473</v>
+        <v>0.481</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5050,7 +5117,7 @@
         <v>79.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
         <v>6.5</v>
@@ -5062,16 +5129,16 @@
         <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
         <v>27.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S26" t="n">
         <v>29.9</v>
@@ -5086,10 +5153,10 @@
         <v>16.3</v>
       </c>
       <c r="W26" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
         <v>5.5</v>
@@ -5101,13 +5168,13 @@
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5128,7 +5195,7 @@
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>14</v>
@@ -5137,7 +5204,7 @@
         <v>17</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5146,16 +5213,16 @@
         <v>6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR26" t="n">
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
@@ -5298,19 +5365,19 @@
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5319,19 +5386,19 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5361,10 +5428,10 @@
         <v>26</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>0.273</v>
+        <v>0.278</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,37 +5478,37 @@
         <v>37.5</v>
       </c>
       <c r="J28" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L28" t="n">
         <v>4.3</v>
       </c>
       <c r="M28" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O28" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U28" t="n">
         <v>21.4</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5492,16 +5559,16 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>27</v>
       </c>
       <c r="AM28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
         <v>28</v>
@@ -5534,10 +5601,10 @@
         <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29" t="n">
         <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.556</v>
+        <v>0.547</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J29" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L29" t="n">
         <v>7.8</v>
       </c>
       <c r="M29" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N29" t="n">
         <v>0.423</v>
@@ -5617,22 +5684,22 @@
         <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V29" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
@@ -5647,13 +5714,13 @@
         <v>18</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5671,13 +5738,13 @@
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
         <v>29</v>
@@ -5701,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>28</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>8</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5847,16 +5914,16 @@
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,13 +5932,13 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
         <v>5</v>
@@ -6047,13 +6114,13 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>3</v>
@@ -6062,7 +6129,7 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6077,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-24-2007-08</t>
+          <t>2008-02-24</t>
         </is>
       </c>
     </row>
